--- a/files/九龙-启德-Grande Monaco.xlsx
+++ b/files/九龙-启德-Grande Monaco.xlsx
@@ -14724,10 +14724,27 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>3/F</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>C | 552呎 (3房)
+$1,400万
+$25,364/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>3&amp;5/F</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>A | 1656呎 (4+房)
 $5,299万
@@ -14735,7 +14752,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>B | 1679呎 (4+房)
 $5,269万
@@ -14743,24 +14760,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 552呎 (3房)
-$1,400万
-$25,364/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="D8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
